--- a/output/pdf_financials_xlsx/KTN.xlsx
+++ b/output/pdf_financials_xlsx/KTN.xlsx
@@ -1433,22 +1433,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.327609</v>
+        <v>-5.327609</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.908559</v>
+        <v>-3.908559</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.581399</v>
+        <v>-2.581399</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>4.838647</v>
+        <v>-4.838647</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>5.889605</v>
+        <v>-5.889605</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>3.528391</v>
+        <v>-3.528391</v>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
@@ -1456,25 +1456,25 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>3.129128</v>
+        <v>-3.129128</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2.466422</v>
+        <v>-2.466422</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.999208</v>
+        <v>-1.999208</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>2.033745</v>
+        <v>-2.033745</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>4.820463</v>
+        <v>-4.820463</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>77.90013</v>
+        <v>-77.90013</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>4.435436</v>
+        <v>-4.435436</v>
       </c>
       <c r="R16" s="1" t="inlineStr">
         <is>
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.327609</v>
+        <v>-5.327609</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.908559</v>
+        <v>-3.908559</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.581399</v>
+        <v>-2.581399</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>4.838647</v>
+        <v>-4.838647</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>5.889605</v>
+        <v>-5.889605</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>3.528391</v>
+        <v>-3.528391</v>
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
@@ -1792,25 +1792,25 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>3.129128</v>
+        <v>-3.129128</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2.466422</v>
+        <v>-2.466422</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.999208</v>
+        <v>-1.999208</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2.033745</v>
+        <v>-2.033745</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>4.820463</v>
+        <v>-4.820463</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>77.90013</v>
+        <v>-77.90013</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>4.435436</v>
+        <v>-4.435436</v>
       </c>
       <c r="R20" s="1" t="inlineStr">
         <is>
@@ -1978,22 +1978,22 @@
         <v>-4.639166</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>5.327609</v>
+        <v>-5.327609</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.908559</v>
+        <v>-3.908559</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.581399</v>
+        <v>-2.581399</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>4.838647</v>
+        <v>-4.838647</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>5.889605</v>
+        <v>-5.889605</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>3.528391</v>
+        <v>-3.528391</v>
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
@@ -2001,25 +2001,25 @@
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>3.129128</v>
+        <v>-3.129128</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2.466422</v>
+        <v>-2.466422</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.999208</v>
+        <v>-1.999208</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.033745</v>
+        <v>-2.033745</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>4.820463</v>
+        <v>-4.820463</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>77.90013</v>
+        <v>-77.90013</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>4.435436</v>
+        <v>-4.435436</v>
       </c>
       <c r="R23" s="1" t="inlineStr">
         <is>
@@ -2191,22 +2191,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-37.518373</v>
+        <v>37.518373</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-44.925966</v>
+        <v>44.925966</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-48.705642</v>
+        <v>48.705642</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-60.483088</v>
+        <v>60.483088</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-66.175337</v>
+        <v>66.175337</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-76.70415199999999</v>
+        <v>76.70415199999999</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-173.840444</v>
+        <v>173.840444</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-189.724769</v>
+        <v>189.724769</v>
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
@@ -2230,13 +2230,13 @@
         </is>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-321.3642</v>
+        <v>321.3642</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-36.064875</v>
+        <v>36.064875</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-44.35436</v>
+        <v>44.35436</v>
       </c>
       <c r="R26" s="1" t="inlineStr">
         <is>
@@ -2266,22 +2266,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>5.282341</v>
+        <v>-5.372877</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.776436</v>
+        <v>-4.040682</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.597339</v>
+        <v>-2.565459</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>4.930007</v>
+        <v>-4.747287</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>5.917942</v>
+        <v>-5.861268</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>3.547961</v>
+        <v>-3.508821</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -2289,25 +2289,25 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>3.239237</v>
+        <v>-3.019019</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>2.58587</v>
+        <v>-2.346974</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.202105</v>
+        <v>-1.796311</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>2.128732</v>
+        <v>-1.938758</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>4.864262</v>
+        <v>-4.776664</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>77.956104</v>
+        <v>-77.844156</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>4.513478</v>
+        <v>-4.357394</v>
       </c>
       <c r="R27" s="1" t="inlineStr">
         <is>
@@ -2408,22 +2408,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>5.328596</v>
+        <v>-5.326622</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.831116</v>
+        <v>-3.986002</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.647107</v>
+        <v>-2.515691</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>4.986936</v>
+        <v>-4.690358</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>5.982922</v>
+        <v>-5.796288</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>3.602786</v>
+        <v>-3.453996</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -2431,25 +2431,25 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>3.27768</v>
+        <v>-2.980576</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>2.626723</v>
+        <v>-2.306121</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.24592</v>
+        <v>-1.752496</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.171294</v>
+        <v>-1.896196</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>4.911734</v>
+        <v>-4.729192</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>77.989408</v>
+        <v>-77.810852</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>4.533827</v>
+        <v>-4.337045</v>
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
@@ -2576,22 +2576,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
@@ -2599,25 +2599,25 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="1" t="inlineStr">
         <is>
@@ -6397,34 +6397,34 @@
         <v>19.886206</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>28.565345</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>30.804341</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>30.983233</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>36.536369</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>37.339396</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>37.267042</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>47.003352</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>50.827629</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>55.366812</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>60.11637</v>
       </c>
     </row>
     <row r="93">
@@ -11258,7 +11258,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -12540,7 +12544,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -13552,7 +13560,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -39098,22 +39110,22 @@
         </is>
       </c>
       <c r="G288" s="5" t="n">
-        <v>5.327609</v>
+        <v>-5.327609</v>
       </c>
       <c r="H288" s="5" t="n">
-        <v>3.908559</v>
+        <v>-3.908559</v>
       </c>
       <c r="I288" s="5" t="n">
-        <v>2.581399</v>
+        <v>-2.581399</v>
       </c>
       <c r="J288" s="5" t="n">
-        <v>4.838647</v>
+        <v>-4.838647</v>
       </c>
       <c r="K288" s="5" t="n">
-        <v>5.889605</v>
+        <v>-5.889605</v>
       </c>
       <c r="L288" s="5" t="n">
-        <v>3.528391</v>
+        <v>-3.528391</v>
       </c>
       <c r="M288" t="inlineStr">
         <is>
@@ -39121,25 +39133,25 @@
         </is>
       </c>
       <c r="N288" s="5" t="n">
-        <v>3.129128</v>
+        <v>-3.129128</v>
       </c>
       <c r="O288" s="5" t="n">
-        <v>2.466422</v>
+        <v>-2.466422</v>
       </c>
       <c r="P288" s="5" t="n">
-        <v>1.999208</v>
+        <v>-1.999208</v>
       </c>
       <c r="Q288" s="5" t="n">
-        <v>2.033745</v>
+        <v>-2.033745</v>
       </c>
       <c r="R288" s="5" t="n">
-        <v>4.820463</v>
+        <v>-4.820463</v>
       </c>
       <c r="S288" s="5" t="n">
-        <v>77.90013</v>
+        <v>-77.90013</v>
       </c>
       <c r="T288" s="5" t="n">
-        <v>4.435436</v>
+        <v>-4.435436</v>
       </c>
       <c r="U288" t="inlineStr">
         <is>
@@ -43534,10 +43546,10 @@
         </is>
       </c>
       <c r="K331" s="5" t="n">
-        <v>5.889605</v>
+        <v>-5.889605</v>
       </c>
       <c r="L331" s="5" t="n">
-        <v>3.528391</v>
+        <v>-3.528391</v>
       </c>
       <c r="M331" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/KTN.xlsx
+++ b/output/pdf_financials_xlsx/KTN.xlsx
@@ -16828,7 +16828,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -17894,7 +17898,11 @@
           <t>Reclamation deposits 51,500</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -19494,7 +19502,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -23706,7 +23718,11 @@
           <t>Decrease in reclamation deposits</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -25392,7 +25408,11 @@
           <t>Decrease in reclamation deposits</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -25714,7 +25734,11 @@
           <t>Increase in reclamation deposits</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -28670,7 +28694,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -30524,7 +30552,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
